--- a/skripsi/data/Templat-Data-KPI-Belum-Tersedia.xlsx
+++ b/skripsi/data/Templat-Data-KPI-Belum-Tersedia.xlsx
@@ -482,7 +482,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TEMPLAT PENGUMPULAN DATA KPI YANG BELUM TERSEDIA – CV PUTRA PONDOK INDAH</t>
+          <t>TEMPLAT PENGUMPULAN DATA KPI YANG BELUM TERSEDIA – CV PUTRA PONDOK INDAH (PERIODE JANUARI–DESEMBER 2025)</t>
         </is>
       </c>
     </row>
@@ -513,7 +513,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Jika data hanya tersedia untuk sebagian periode (misalnya 2025 saja), cukup isi periode tersebut.</t>
+          <t>Periode data: Januari–Desember 2025, sama dengan periode data pada Bab I dan Bab IV.</t>
         </is>
       </c>
     </row>
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -686,7 +686,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
@@ -724,7 +724,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -762,7 +762,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -911,918 +911,6 @@
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="8" t="n"/>
       <c r="K17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="8" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="8" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
-      <c r="J45" s="8" t="n"/>
-      <c r="K45" s="8" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
-      <c r="J48" s="8" t="n"/>
-      <c r="K48" s="8" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="8" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
-      <c r="G50" s="8" t="n"/>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="8" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="n"/>
-      <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="8" t="n"/>
-      <c r="J52" s="8" t="n"/>
-      <c r="K52" s="8" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="8" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
-      <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
-      <c r="J54" s="8" t="n"/>
-      <c r="K54" s="8" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
-      <c r="J55" s="8" t="n"/>
-      <c r="K55" s="8" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
-      <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
-      <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="8" t="n"/>
-      <c r="J56" s="8" t="n"/>
-      <c r="K56" s="8" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
-      <c r="J57" s="8" t="n"/>
-      <c r="K57" s="8" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
-      <c r="J58" s="8" t="n"/>
-      <c r="K58" s="8" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="8" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
-      <c r="I60" s="8" t="n"/>
-      <c r="J60" s="8" t="n"/>
-      <c r="K60" s="8" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="8" t="n"/>
-      <c r="J61" s="8" t="n"/>
-      <c r="K61" s="8" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="8" t="n"/>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="8" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
-      <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="8" t="n"/>
-      <c r="J65" s="8" t="n"/>
-      <c r="K65" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1870,7 +958,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Satu baris = satu pesanan. Jika data lengkap tidak ada, catat pesanan selama periode penelitian atau ambil sampel dari nota/buku pesanan.</t>
+          <t>Satu baris = satu pesanan pada tahun 2025. Jika data lengkap tidak ada, ambil sampel pesanan dari nota/buku pesanan 2025 dan sebutkan jumlah sampelnya.</t>
         </is>
       </c>
     </row>
@@ -3340,7 +2428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3436,7 +2524,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -3455,7 +2543,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
@@ -3474,7 +2562,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -3493,7 +2581,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -3512,7 +2600,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -3531,7 +2619,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -3550,7 +2638,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -3569,7 +2657,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -3588,7 +2676,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -3607,7 +2695,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -3626,7 +2714,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -3645,7 +2733,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -3661,918 +2749,6 @@
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="8" t="n"/>
       <c r="K17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-      <c r="J38" s="8" t="n"/>
-      <c r="K38" s="8" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
-      <c r="J39" s="8" t="n"/>
-      <c r="K39" s="8" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-      <c r="J40" s="8" t="n"/>
-      <c r="K40" s="8" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-      <c r="J41" s="8" t="n"/>
-      <c r="K41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-      <c r="J42" s="8" t="n"/>
-      <c r="K42" s="8" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
-      <c r="J43" s="8" t="n"/>
-      <c r="K43" s="8" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-      <c r="J44" s="8" t="n"/>
-      <c r="K44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
-      <c r="J45" s="8" t="n"/>
-      <c r="K45" s="8" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
-      <c r="J46" s="8" t="n"/>
-      <c r="K46" s="8" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-      <c r="J47" s="8" t="n"/>
-      <c r="K47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
-      <c r="J48" s="8" t="n"/>
-      <c r="K48" s="8" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-      <c r="J49" s="8" t="n"/>
-      <c r="K49" s="8" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
-      <c r="G50" s="8" t="n"/>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
-      <c r="J50" s="8" t="n"/>
-      <c r="K50" s="8" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-      <c r="J51" s="8" t="n"/>
-      <c r="K51" s="8" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="n"/>
-      <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="8" t="n"/>
-      <c r="J52" s="8" t="n"/>
-      <c r="K52" s="8" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-      <c r="J53" s="8" t="n"/>
-      <c r="K53" s="8" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
-      <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
-      <c r="J54" s="8" t="n"/>
-      <c r="K54" s="8" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
-      <c r="J55" s="8" t="n"/>
-      <c r="K55" s="8" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
-      <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
-      <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="8" t="n"/>
-      <c r="J56" s="8" t="n"/>
-      <c r="K56" s="8" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
-      <c r="J57" s="8" t="n"/>
-      <c r="K57" s="8" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
-      <c r="J58" s="8" t="n"/>
-      <c r="K58" s="8" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-      <c r="J59" s="8" t="n"/>
-      <c r="K59" s="8" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
-      <c r="I60" s="8" t="n"/>
-      <c r="J60" s="8" t="n"/>
-      <c r="K60" s="8" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="8" t="n"/>
-      <c r="J61" s="8" t="n"/>
-      <c r="K61" s="8" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-      <c r="J62" s="8" t="n"/>
-      <c r="K62" s="8" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="8" t="n"/>
-      <c r="J63" s="8" t="n"/>
-      <c r="K63" s="8" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-      <c r="J64" s="8" t="n"/>
-      <c r="K64" s="8" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
-      <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="8" t="n"/>
-      <c r="J65" s="8" t="n"/>
-      <c r="K65" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4588,7 +2764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -4672,7 +2848,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -4689,7 +2865,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
@@ -4706,7 +2882,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -4723,7 +2899,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -4740,7 +2916,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -4757,7 +2933,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -4774,7 +2950,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -4791,7 +2967,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -4808,7 +2984,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -4825,7 +3001,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -4842,7 +3018,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -4859,7 +3035,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -4873,822 +3049,6 @@
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
       <c r="I17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
-      <c r="G50" s="8" t="n"/>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="n"/>
-      <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="8" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
-      <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
-      <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
-      <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="8" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
-      <c r="I60" s="8" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="8" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="8" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
-      <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5704,7 +3064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -5735,7 +3095,7 @@
     <row r="3" ht="45" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Total produksi dapat diambil dari sheet 1_REKAP_ML_INPUT. Q3 dihitung dari defect rate beberapa bulan, sehingga minimal diperlukan data beberapa bulan berturut-turut.</t>
+          <t>Total produksi dapat diambil dari Tabel 4.12 (sheet 1_REKAP_ML_INPUT, tahun 2025). Q3 dihitung dari defect rate beberapa bulan, sehingga diperlukan data beberapa bulan berturut-turut pada 2025.</t>
         </is>
       </c>
     </row>
@@ -5788,7 +3148,7 @@
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -5805,7 +3165,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
@@ -5822,7 +3182,7 @@
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
@@ -5839,7 +3199,7 @@
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
@@ -5856,7 +3216,7 @@
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
@@ -5873,7 +3233,7 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
@@ -5890,7 +3250,7 @@
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
@@ -5907,7 +3267,7 @@
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -5924,7 +3284,7 @@
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
@@ -5941,7 +3301,7 @@
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
@@ -5958,7 +3318,7 @@
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
@@ -5975,7 +3335,7 @@
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -5989,822 +3349,6 @@
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="8" t="n"/>
       <c r="I17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="8" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="8" t="n"/>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="8" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="8" t="n"/>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="8" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="n"/>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="n"/>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="8" t="n"/>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="8" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="8" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="8" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="8" t="n"/>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="8" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="8" t="n"/>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="8" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="8" t="n"/>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="8" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="8" t="n"/>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="8" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="n"/>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="8" t="n"/>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="8" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="n"/>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="8" t="n"/>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="8" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="n"/>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="8" t="n"/>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="8" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="8" t="n"/>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="8" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="8" t="n"/>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="8" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="8" t="n"/>
-      <c r="H38" s="8" t="n"/>
-      <c r="I38" s="8" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n"/>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="8" t="n"/>
-      <c r="H39" s="8" t="n"/>
-      <c r="I39" s="8" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n"/>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="8" t="n"/>
-      <c r="H40" s="8" t="n"/>
-      <c r="I40" s="8" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="n"/>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="8" t="n"/>
-      <c r="H41" s="8" t="n"/>
-      <c r="I41" s="8" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n"/>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="8" t="n"/>
-      <c r="H42" s="8" t="n"/>
-      <c r="I42" s="8" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C43" s="8" t="n"/>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="8" t="n"/>
-      <c r="H43" s="8" t="n"/>
-      <c r="I43" s="8" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C44" s="8" t="n"/>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="8" t="n"/>
-      <c r="H44" s="8" t="n"/>
-      <c r="I44" s="8" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C45" s="8" t="n"/>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="8" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="8" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="8" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="8" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C47" s="8" t="n"/>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="8" t="n"/>
-      <c r="H47" s="8" t="n"/>
-      <c r="I47" s="8" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n"/>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="8" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="8" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="8" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="8" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n"/>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
-      <c r="G50" s="8" t="n"/>
-      <c r="H50" s="8" t="n"/>
-      <c r="I50" s="8" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="n"/>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="8" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="8" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="n"/>
-      <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="n"/>
-      <c r="G52" s="8" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="8" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="7" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="8" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B54" s="7" t="inlineStr">
-        <is>
-          <t>Januari</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="n"/>
-      <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="8" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="8" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B55" s="7" t="inlineStr">
-        <is>
-          <t>Februari</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="8" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="8" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B56" s="7" t="inlineStr">
-        <is>
-          <t>Maret</t>
-        </is>
-      </c>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="n"/>
-      <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
-      <c r="G56" s="8" t="n"/>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="8" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="n"/>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="8" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="8" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>Mei</t>
-        </is>
-      </c>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="n"/>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="8" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="8" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>Juni</t>
-        </is>
-      </c>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="n"/>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="8" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="8" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>Juli</t>
-        </is>
-      </c>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="n"/>
-      <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="8" t="n"/>
-      <c r="H60" s="8" t="n"/>
-      <c r="I60" s="8" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Agustus</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="8" t="n"/>
-      <c r="H61" s="8" t="n"/>
-      <c r="I61" s="8" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>September</t>
-        </is>
-      </c>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="n"/>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="8" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="8" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B63" s="7" t="inlineStr">
-        <is>
-          <t>Oktober</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="n"/>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="8" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="8" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="n"/>
-      <c r="F64" s="8" t="n"/>
-      <c r="G64" s="8" t="n"/>
-      <c r="H64" s="8" t="n"/>
-      <c r="I64" s="8" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="7" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B65" s="7" t="inlineStr">
-        <is>
-          <t>Desember</t>
-        </is>
-      </c>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="8" t="n"/>
-      <c r="F65" s="8" t="n"/>
-      <c r="G65" s="8" t="n"/>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="8" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
